--- a/fa25biomass1.xlsx
+++ b/fa25biomass1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528DFC55-E64F-4DC7-9EE5-FE13D5072F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E312DA-A1E8-48F6-81E4-E4490328D50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
   </bookViews>
   <sheets>
     <sheet name="fa25biomass1" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
     <t>Beetle</t>
   </si>
   <si>
-    <t>Control</t>
-  </si>
-  <si>
     <t>C-Sb-1</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>Microplastic</t>
-  </si>
-  <si>
     <t>Seed_weight</t>
   </si>
   <si>
@@ -195,6 +189,12 @@
   </si>
   <si>
     <t>No beetle</t>
+  </si>
+  <si>
+    <t>Control,</t>
+  </si>
+  <si>
+    <t>Microplastic,</t>
   </si>
 </sst>
 </file>
@@ -230,9 +230,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,33 +580,33 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" t="s">
-        <v>50</v>
-      </c>
       <c r="H1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
       </c>
       <c r="D2">
         <v>19.13</v>
@@ -627,13 +626,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>16.14</v>
@@ -653,13 +652,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>17.059999999999999</v>
@@ -679,13 +678,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>21.25</v>
@@ -705,13 +704,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>15.62</v>
@@ -725,19 +724,19 @@
       <c r="G6">
         <v>6.2</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>4.09</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>12.96</v>
@@ -757,13 +756,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>20.39</v>
@@ -783,13 +782,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>16.86</v>
@@ -809,13 +808,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>14.27</v>
@@ -835,13 +834,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>20.260000000000002</v>
@@ -861,13 +860,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <v>17.66</v>
@@ -887,13 +886,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>13.21</v>
@@ -913,13 +912,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>19.309999999999999</v>
@@ -939,13 +938,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>14.6</v>
@@ -965,13 +964,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>16.010000000000002</v>
@@ -991,13 +990,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17">
         <v>13.86</v>
@@ -1017,13 +1016,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18">
         <v>21.03</v>
@@ -1043,13 +1042,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>21.13</v>
@@ -1069,13 +1068,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>18.87</v>
@@ -1095,13 +1094,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21">
         <v>6.64</v>
@@ -1121,13 +1120,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22">
         <v>17.72</v>
@@ -1147,13 +1146,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23">
         <v>22.36</v>
@@ -1173,13 +1172,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24">
         <v>23.71</v>
@@ -1199,13 +1198,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25">
         <v>26.15</v>
@@ -1225,13 +1224,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26">
         <v>23.9</v>
@@ -1251,13 +1250,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27">
         <v>33.450000000000003</v>
@@ -1277,13 +1276,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>29.25</v>
@@ -1303,13 +1302,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>45.98</v>
@@ -1329,13 +1328,13 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30">
         <v>24.51</v>
@@ -1355,13 +1354,13 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31">
         <v>22.54</v>
@@ -1381,13 +1380,13 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32">
         <v>34.549999999999997</v>
@@ -1407,13 +1406,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>26.59</v>
@@ -1433,13 +1432,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>25.19</v>
@@ -1459,13 +1458,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35">
         <v>25.35</v>
@@ -1485,13 +1484,13 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36">
         <v>26.7</v>
@@ -1511,13 +1510,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37">
         <v>26.14</v>
@@ -1537,13 +1536,13 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38">
         <v>21.15</v>
@@ -1563,13 +1562,13 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39">
         <v>27.22</v>
@@ -1589,13 +1588,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40">
         <v>29.37</v>
@@ -1615,13 +1614,13 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41">
         <v>33.450000000000003</v>
@@ -1641,13 +1640,13 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42">
         <v>34.42</v>
@@ -1667,13 +1666,13 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43">
         <v>29.57</v>
@@ -1700,11 +1699,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1941,27 +1941,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1986,9 +1976,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
